--- a/src/video_generator/SHORTS/Roteiros/roteiro_versiculos.xlsx
+++ b/src/video_generator/SHORTS/Roteiros/roteiro_versiculos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\src\video_generator\SHORTS\Roteiros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FB9F79-0EDE-417A-BFB9-DF34048B7262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DFFFED-DB5E-4B5C-8CDF-FE459DC9444C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -518,12 +518,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -553,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -570,6 +582,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -873,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="4" bestFit="1" customWidth="1"/>
@@ -905,183 +934,183 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="F2" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="F3" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="F8" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="F9" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1325,203 +1354,203 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="F23" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="F24" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="F25" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="F26" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="F27" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="F28" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="F29" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="F30" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="F31" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1743,6 +1772,17 @@
       </c>
       <c r="F43" s="6" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D46" s="6">
+        <v>9</v>
+      </c>
+      <c r="E46" s="6">
+        <v>15</v>
+      </c>
+      <c r="F46" s="6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
